--- a/tables/xls/it/91_Servizi.xlsx
+++ b/tables/xls/it/91_Servizi.xlsx
@@ -16,14 +16,68 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="84">
   <si>
     <t>NOME</t>
   </si>
   <si>
+    <t>DESCRIZIONE</t>
+  </si>
+  <si>
     <t>INTERVENTO</t>
   </si>
   <si>
+    <t>STATO</t>
+  </si>
+  <si>
+    <t>INIZIO</t>
+  </si>
+  <si>
+    <t>FINE</t>
+  </si>
+  <si>
+    <t>DATA/ORA SOPRALLUOGO</t>
+  </si>
+  <si>
+    <t>COMUNE</t>
+  </si>
+  <si>
+    <t>PROVINCIA</t>
+  </si>
+  <si>
+    <t>INDIRIZZO</t>
+  </si>
+  <si>
+    <t>SQUADRE ATTIVATE</t>
+  </si>
+  <si>
+    <t>OPERATORI A SUPPORTO</t>
+  </si>
+  <si>
+    <t>DATA ORA SEGNALAZIONE</t>
+  </si>
+  <si>
+    <t>RIFERIMENTO VVF</t>
+  </si>
+  <si>
+    <t>NOME SEGNALANTE</t>
+  </si>
+  <si>
+    <t>QUALIFICA SEGNALANTE</t>
+  </si>
+  <si>
+    <t>INDIRIZZO SEGNALANTE</t>
+  </si>
+  <si>
+    <t>TELEFONO SEGNALANTE</t>
+  </si>
+  <si>
+    <t>LATITUDINE</t>
+  </si>
+  <si>
+    <t>LONGITUDINE</t>
+  </si>
+  <si>
     <t>ORDINE</t>
   </si>
   <si>
@@ -33,33 +87,6 @@
     <t>COLORE</t>
   </si>
   <si>
-    <t>DESCRIZIONE</t>
-  </si>
-  <si>
-    <t>LATITUDINE</t>
-  </si>
-  <si>
-    <t>LONGITUDINE</t>
-  </si>
-  <si>
-    <t>COMUNE</t>
-  </si>
-  <si>
-    <t>PROVINCIA</t>
-  </si>
-  <si>
-    <t>INDIRIZZO</t>
-  </si>
-  <si>
-    <t>INIZIO</t>
-  </si>
-  <si>
-    <t>FINE</t>
-  </si>
-  <si>
-    <t>OPERATORI A SUPPORTO</t>
-  </si>
-  <si>
     <t>NOTE</t>
   </si>
   <si>
@@ -135,6 +162,9 @@
     <t>Categoria</t>
   </si>
   <si>
+    <t>Filtro visibilità</t>
+  </si>
+  <si>
     <t>Testo</t>
   </si>
   <si>
@@ -144,12 +174,75 @@
     <t>No</t>
   </si>
   <si>
+    <t>Testo Lungo</t>
+  </si>
+  <si>
     <t>Testo - Elenco di valori</t>
   </si>
   <si>
     <t>,SI,NO</t>
   </si>
   <si>
+    <t>,Segnalato,In corso,Concluso</t>
+  </si>
+  <si>
+    <t>Stato di avanzamento dell'intervento</t>
+  </si>
+  <si>
+    <t>Data e ora</t>
+  </si>
+  <si>
+    <t>Data e ora del sopralluogo per la definizione dell'intervento</t>
+  </si>
+  <si>
+    <t>[segreteriacampo_it_city]</t>
+  </si>
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>province</t>
+  </si>
+  <si>
+    <t>Squadre/gruppi attivati, una per riga</t>
+  </si>
+  <si>
+    <t>Data e ora in cui è arrivata la segnalazione (diversa da INIZIO, che è l'avvio dell'intervento)</t>
+  </si>
+  <si>
+    <t>RIF. VVF</t>
+  </si>
+  <si>
+    <t>Numero di riferimento dei Vigili del Fuoco, se presente</t>
+  </si>
+  <si>
+    <t>Nome e cognome del segnalante</t>
+  </si>
+  <si>
+    <t>,Sindaco,Sala Operativa VVF,Prefettura,Provincia,Coordinatore GC,Polizia Locale,Cittadino,Altro</t>
+  </si>
+  <si>
+    <t>Ruolo di chi ha effettuato la segnalazione</t>
+  </si>
+  <si>
+    <t>TEL. SEGNALANTE</t>
+  </si>
+  <si>
+    <t>Numero di telefono del segnalante</t>
+  </si>
+  <si>
+    <t>Numero Decimale</t>
+  </si>
+  <si>
+    <t>lat</t>
+  </si>
+  <si>
+    <t>Coordinate in Gradi Decimali (Decimal Degrees - DD). In questo formato, sia la latitudine che la longitudine sono rappresentate come numeri decimali. Esempio: Latitudine: 41.40338, Longitudine: 2.17403.</t>
+  </si>
+  <si>
+    <t>lon</t>
+  </si>
+  <si>
     <t>Numero Intero</t>
   </si>
   <si>
@@ -163,33 +256,6 @@
   </si>
   <si>
     <t>Verrà utilizzato per identificare il servizio sulla mappa</t>
-  </si>
-  <si>
-    <t>Testo Lungo</t>
-  </si>
-  <si>
-    <t>Numero Decimale</t>
-  </si>
-  <si>
-    <t>[segreteriacampo_it_city]</t>
-  </si>
-  <si>
-    <t>lat</t>
-  </si>
-  <si>
-    <t>Coordinate in Gradi Decimali (Decimal Degrees - DD). In questo formato, sia la latitudine che la longitudine sono rappresentate come numeri decimali. Esempio: Latitudine: 41.40338, Longitudine: 2.17403.</t>
-  </si>
-  <si>
-    <t>lon</t>
-  </si>
-  <si>
-    <t>name</t>
-  </si>
-  <si>
-    <t>province</t>
-  </si>
-  <si>
-    <t>Data e ora</t>
   </si>
   <si>
     <t>SERVIZI</t>
@@ -541,27 +607,36 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:O1"/>
+  <dimension ref="A1:X1"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="5.856" bestFit="true" customWidth="true" style="0"/>
-    <col min="2" max="2" width="12.854" bestFit="true" customWidth="true" style="0"/>
-    <col min="3" max="3" width="8.141" bestFit="true" customWidth="true" style="0"/>
-    <col min="4" max="4" width="9.283" bestFit="true" customWidth="true" style="0"/>
+    <col min="2" max="2" width="13.997" bestFit="true" customWidth="true" style="0"/>
+    <col min="3" max="3" width="12.854" bestFit="true" customWidth="true" style="0"/>
+    <col min="4" max="4" width="6.998" bestFit="true" customWidth="true" style="0"/>
     <col min="5" max="5" width="8.141" bestFit="true" customWidth="true" style="0"/>
-    <col min="6" max="6" width="13.997" bestFit="true" customWidth="true" style="0"/>
-    <col min="7" max="7" width="12.854" bestFit="true" customWidth="true" style="0"/>
-    <col min="8" max="8" width="13.997" bestFit="true" customWidth="true" style="0"/>
-    <col min="9" max="9" width="8.141" bestFit="true" customWidth="true" style="0"/>
+    <col min="6" max="6" width="5.856" bestFit="true" customWidth="true" style="0"/>
+    <col min="7" max="7" width="24.708" bestFit="true" customWidth="true" style="0"/>
+    <col min="8" max="8" width="8.141" bestFit="true" customWidth="true" style="0"/>
+    <col min="9" max="9" width="11.711" bestFit="true" customWidth="true" style="0"/>
     <col min="10" max="10" width="11.711" bestFit="true" customWidth="true" style="0"/>
-    <col min="11" max="11" width="11.711" bestFit="true" customWidth="true" style="0"/>
-    <col min="12" max="12" width="8.141" bestFit="true" customWidth="true" style="0"/>
-    <col min="13" max="13" width="5.856" bestFit="true" customWidth="true" style="0"/>
-    <col min="14" max="14" width="24.708" bestFit="true" customWidth="true" style="0"/>
-    <col min="15" max="15" width="5.856" bestFit="true" customWidth="true" style="0"/>
+    <col min="11" max="11" width="19.995" bestFit="true" customWidth="true" style="0"/>
+    <col min="12" max="12" width="24.708" bestFit="true" customWidth="true" style="0"/>
+    <col min="13" max="13" width="25.851" bestFit="true" customWidth="true" style="0"/>
+    <col min="14" max="14" width="18.71" bestFit="true" customWidth="true" style="0"/>
+    <col min="15" max="15" width="18.71" bestFit="true" customWidth="true" style="0"/>
+    <col min="16" max="16" width="24.708" bestFit="true" customWidth="true" style="0"/>
+    <col min="17" max="17" width="24.708" bestFit="true" customWidth="true" style="0"/>
+    <col min="18" max="18" width="23.423" bestFit="true" customWidth="true" style="0"/>
+    <col min="19" max="19" width="12.854" bestFit="true" customWidth="true" style="0"/>
+    <col min="20" max="20" width="13.997" bestFit="true" customWidth="true" style="0"/>
+    <col min="21" max="21" width="8.141" bestFit="true" customWidth="true" style="0"/>
+    <col min="22" max="22" width="9.283" bestFit="true" customWidth="true" style="0"/>
+    <col min="23" max="23" width="8.141" bestFit="true" customWidth="true" style="0"/>
+    <col min="24" max="24" width="5.856" bestFit="true" customWidth="true" style="0"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:24">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -606,6 +681,33 @@
       </c>
       <c r="O1" t="s">
         <v>14</v>
+      </c>
+      <c r="P1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -620,10 +722,10 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:P25"/>
+  <dimension ref="A1:Y26"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
-    <row r="1" spans="1:16">
+    <row r="1" spans="1:25">
       <c r="B1" t="s">
         <v>0</v>
       </c>
@@ -669,10 +771,37 @@
       <c r="P1" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="2" spans="1:16">
+      <c r="Q1" t="s">
+        <v>15</v>
+      </c>
+      <c r="R1" t="s">
+        <v>16</v>
+      </c>
+      <c r="S1" t="s">
+        <v>17</v>
+      </c>
+      <c r="T1" t="s">
+        <v>18</v>
+      </c>
+      <c r="U1" t="s">
+        <v>19</v>
+      </c>
+      <c r="V1" t="s">
+        <v>20</v>
+      </c>
+      <c r="W1" t="s">
+        <v>21</v>
+      </c>
+      <c r="X1" t="s">
+        <v>22</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2" spans="1:25">
       <c r="A2" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="B2">
         <v>1</v>
@@ -687,42 +816,69 @@
         <v>4</v>
       </c>
       <c r="F2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L2">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="M2">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="N2">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="O2">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="P2">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16">
+        <v>19</v>
+      </c>
+      <c r="Q2">
+        <v>20</v>
+      </c>
+      <c r="R2">
+        <v>21</v>
+      </c>
+      <c r="S2">
+        <v>22</v>
+      </c>
+      <c r="T2">
+        <v>30</v>
+      </c>
+      <c r="U2">
+        <v>31</v>
+      </c>
+      <c r="V2">
+        <v>80</v>
+      </c>
+      <c r="W2">
+        <v>81</v>
+      </c>
+      <c r="X2">
+        <v>82</v>
+      </c>
+      <c r="Y2">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="3" spans="1:25">
       <c r="A3" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="B3" t="s">
         <v>0</v>
@@ -764,51 +920,78 @@
         <v>12</v>
       </c>
       <c r="O3" t="s">
-        <v>13</v>
+        <v>64</v>
       </c>
       <c r="P3" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="4" spans="1:16">
+      <c r="Q3" t="s">
+        <v>15</v>
+      </c>
+      <c r="R3" t="s">
+        <v>16</v>
+      </c>
+      <c r="S3" t="s">
+        <v>69</v>
+      </c>
+      <c r="T3" t="s">
+        <v>18</v>
+      </c>
+      <c r="U3" t="s">
+        <v>19</v>
+      </c>
+      <c r="V3" t="s">
+        <v>20</v>
+      </c>
+      <c r="W3" t="s">
+        <v>21</v>
+      </c>
+      <c r="X3" t="s">
+        <v>22</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="4" spans="1:25">
       <c r="A4" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="B4" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="C4" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="D4" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="E4" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="F4" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="G4" t="s">
+        <v>57</v>
+      </c>
+      <c r="H4" t="s">
+        <v>57</v>
+      </c>
+      <c r="I4" t="s">
         <v>49</v>
       </c>
-      <c r="H4" t="s">
-        <v>50</v>
-      </c>
-      <c r="I4" t="s">
-        <v>50</v>
-      </c>
       <c r="J4" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="K4" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="L4" t="s">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="M4" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="N4" t="s">
         <v>57</v>
@@ -817,424 +1000,639 @@
         <v>49</v>
       </c>
       <c r="P4" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>53</v>
+      </c>
+      <c r="R4" t="s">
+        <v>49</v>
+      </c>
+      <c r="S4" t="s">
+        <v>49</v>
+      </c>
+      <c r="T4" t="s">
+        <v>71</v>
+      </c>
+      <c r="U4" t="s">
+        <v>71</v>
+      </c>
+      <c r="V4" t="s">
+        <v>75</v>
+      </c>
+      <c r="W4" t="s">
+        <v>49</v>
+      </c>
+      <c r="X4" t="s">
+        <v>53</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="5" spans="1:25">
+      <c r="A5" t="s">
+        <v>27</v>
+      </c>
+      <c r="D5" t="s">
+        <v>54</v>
+      </c>
+      <c r="E5" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>67</v>
+      </c>
+      <c r="X5" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="6" spans="1:25">
+      <c r="A6" t="s">
+        <v>28</v>
+      </c>
+      <c r="B6">
+        <v>255</v>
+      </c>
+      <c r="C6">
+        <v>255</v>
+      </c>
+      <c r="D6">
+        <v>255</v>
+      </c>
+      <c r="E6">
+        <v>255</v>
+      </c>
+      <c r="F6">
+        <v>255</v>
+      </c>
+      <c r="G6">
+        <v>255</v>
+      </c>
+      <c r="H6">
+        <v>255</v>
+      </c>
+      <c r="I6">
+        <v>255</v>
+      </c>
+      <c r="J6">
+        <v>255</v>
+      </c>
+      <c r="K6">
+        <v>255</v>
+      </c>
+      <c r="L6">
+        <v>255</v>
+      </c>
+      <c r="M6">
+        <v>255</v>
+      </c>
+      <c r="N6">
+        <v>255</v>
+      </c>
+      <c r="O6">
+        <v>255</v>
+      </c>
+      <c r="P6">
+        <v>255</v>
+      </c>
+      <c r="Q6">
+        <v>255</v>
+      </c>
+      <c r="R6">
+        <v>255</v>
+      </c>
+      <c r="S6">
+        <v>255</v>
+      </c>
+      <c r="T6">
+        <v>255</v>
+      </c>
+      <c r="U6">
+        <v>255</v>
+      </c>
+      <c r="V6">
+        <v>255</v>
+      </c>
+      <c r="W6">
+        <v>1</v>
+      </c>
+      <c r="X6">
+        <v>255</v>
+      </c>
+      <c r="Y6">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="7" spans="1:25">
+      <c r="A7" t="s">
+        <v>29</v>
+      </c>
+      <c r="B7" t="s">
+        <v>50</v>
+      </c>
+      <c r="C7" t="s">
+        <v>51</v>
+      </c>
+      <c r="D7" t="s">
+        <v>51</v>
+      </c>
+      <c r="E7" t="s">
+        <v>51</v>
+      </c>
+      <c r="F7" t="s">
+        <v>51</v>
+      </c>
+      <c r="G7" t="s">
+        <v>51</v>
+      </c>
+      <c r="H7" t="s">
+        <v>51</v>
+      </c>
+      <c r="I7" t="s">
+        <v>51</v>
+      </c>
+      <c r="J7" t="s">
+        <v>51</v>
+      </c>
+      <c r="K7" t="s">
+        <v>51</v>
+      </c>
+      <c r="L7" t="s">
+        <v>51</v>
+      </c>
+      <c r="M7" t="s">
+        <v>51</v>
+      </c>
+      <c r="N7" t="s">
+        <v>51</v>
+      </c>
+      <c r="O7" t="s">
+        <v>51</v>
+      </c>
+      <c r="P7" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>51</v>
+      </c>
+      <c r="R7" t="s">
+        <v>51</v>
+      </c>
+      <c r="S7" t="s">
+        <v>51</v>
+      </c>
+      <c r="T7" t="s">
+        <v>51</v>
+      </c>
+      <c r="U7" t="s">
+        <v>51</v>
+      </c>
+      <c r="V7" t="s">
+        <v>50</v>
+      </c>
+      <c r="W7" t="s">
+        <v>51</v>
+      </c>
+      <c r="X7" t="s">
+        <v>51</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25">
+      <c r="A8" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25">
+      <c r="A9" t="s">
+        <v>31</v>
+      </c>
+      <c r="B9" t="s">
+        <v>51</v>
+      </c>
+      <c r="C9" t="s">
+        <v>51</v>
+      </c>
+      <c r="D9" t="s">
+        <v>51</v>
+      </c>
+      <c r="E9" t="s">
+        <v>51</v>
+      </c>
+      <c r="F9" t="s">
+        <v>51</v>
+      </c>
+      <c r="G9" t="s">
+        <v>51</v>
+      </c>
+      <c r="H9" t="s">
+        <v>51</v>
+      </c>
+      <c r="I9" t="s">
+        <v>51</v>
+      </c>
+      <c r="J9" t="s">
+        <v>51</v>
+      </c>
+      <c r="K9" t="s">
+        <v>51</v>
+      </c>
+      <c r="L9" t="s">
+        <v>51</v>
+      </c>
+      <c r="M9" t="s">
+        <v>51</v>
+      </c>
+      <c r="N9" t="s">
+        <v>51</v>
+      </c>
+      <c r="O9" t="s">
+        <v>51</v>
+      </c>
+      <c r="P9" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>51</v>
+      </c>
+      <c r="R9" t="s">
+        <v>51</v>
+      </c>
+      <c r="S9" t="s">
+        <v>51</v>
+      </c>
+      <c r="T9" t="s">
+        <v>51</v>
+      </c>
+      <c r="U9" t="s">
+        <v>51</v>
+      </c>
+      <c r="V9" t="s">
+        <v>51</v>
+      </c>
+      <c r="W9" t="s">
+        <v>51</v>
+      </c>
+      <c r="X9" t="s">
+        <v>51</v>
+      </c>
+      <c r="Y9" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25">
+      <c r="A10" t="s">
+        <v>32</v>
+      </c>
+      <c r="B10" t="s">
+        <v>50</v>
+      </c>
+      <c r="C10" t="s">
+        <v>50</v>
+      </c>
+      <c r="D10" t="s">
+        <v>50</v>
+      </c>
+      <c r="E10" t="s">
+        <v>50</v>
+      </c>
+      <c r="F10" t="s">
+        <v>50</v>
+      </c>
+      <c r="G10" t="s">
+        <v>50</v>
+      </c>
+      <c r="H10" t="s">
+        <v>50</v>
+      </c>
+      <c r="I10" t="s">
+        <v>50</v>
+      </c>
+      <c r="J10" t="s">
+        <v>50</v>
+      </c>
+      <c r="K10" t="s">
+        <v>50</v>
+      </c>
+      <c r="L10" t="s">
+        <v>50</v>
+      </c>
+      <c r="M10" t="s">
+        <v>50</v>
+      </c>
+      <c r="N10" t="s">
+        <v>50</v>
+      </c>
+      <c r="O10" t="s">
+        <v>50</v>
+      </c>
+      <c r="P10" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>50</v>
+      </c>
+      <c r="R10" t="s">
+        <v>50</v>
+      </c>
+      <c r="S10" t="s">
+        <v>50</v>
+      </c>
+      <c r="T10" t="s">
+        <v>50</v>
+      </c>
+      <c r="U10" t="s">
+        <v>50</v>
+      </c>
+      <c r="V10" t="s">
+        <v>50</v>
+      </c>
+      <c r="W10" t="s">
+        <v>50</v>
+      </c>
+      <c r="X10" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y10" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25">
+      <c r="A11" t="s">
+        <v>33</v>
+      </c>
+      <c r="E11" t="s">
+        <v>51</v>
+      </c>
+      <c r="O11" t="s">
+        <v>51</v>
+      </c>
+      <c r="P11" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>51</v>
+      </c>
+      <c r="R11" t="s">
+        <v>51</v>
+      </c>
+      <c r="S11" t="s">
+        <v>51</v>
+      </c>
+      <c r="T11" t="s">
+        <v>51</v>
+      </c>
+      <c r="U11" t="s">
+        <v>51</v>
+      </c>
+      <c r="V11" t="s">
+        <v>51</v>
+      </c>
+      <c r="W11" t="s">
+        <v>51</v>
+      </c>
+      <c r="X11" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="12" spans="1:25">
+      <c r="A12" t="s">
+        <v>34</v>
+      </c>
+      <c r="B12" t="s">
+        <v>51</v>
+      </c>
+      <c r="C12" t="s">
+        <v>51</v>
+      </c>
+      <c r="D12" t="s">
+        <v>51</v>
+      </c>
+      <c r="E12" t="s">
+        <v>51</v>
+      </c>
+      <c r="F12" t="s">
+        <v>51</v>
+      </c>
+      <c r="G12" t="s">
+        <v>51</v>
+      </c>
+      <c r="H12" t="s">
+        <v>51</v>
+      </c>
+      <c r="I12" t="s">
+        <v>51</v>
+      </c>
+      <c r="J12" t="s">
+        <v>51</v>
+      </c>
+      <c r="K12" t="s">
+        <v>51</v>
+      </c>
+      <c r="L12" t="s">
+        <v>51</v>
+      </c>
+      <c r="M12" t="s">
+        <v>51</v>
+      </c>
+      <c r="N12" t="s">
+        <v>51</v>
+      </c>
+      <c r="O12" t="s">
+        <v>51</v>
+      </c>
+      <c r="P12" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>51</v>
+      </c>
+      <c r="R12" t="s">
+        <v>51</v>
+      </c>
+      <c r="S12" t="s">
+        <v>51</v>
+      </c>
+      <c r="T12" t="s">
+        <v>51</v>
+      </c>
+      <c r="U12" t="s">
+        <v>51</v>
+      </c>
+      <c r="V12" t="s">
+        <v>51</v>
+      </c>
+      <c r="W12" t="s">
+        <v>51</v>
+      </c>
+      <c r="X12" t="s">
+        <v>51</v>
+      </c>
+      <c r="Y12" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25">
+      <c r="A13" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25">
+      <c r="A14" t="s">
+        <v>36</v>
+      </c>
+      <c r="I14" t="s">
+        <v>59</v>
+      </c>
+      <c r="J14" t="s">
+        <v>59</v>
+      </c>
+      <c r="T14" t="s">
+        <v>59</v>
+      </c>
+      <c r="U14" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25">
+      <c r="A15" t="s">
+        <v>37</v>
+      </c>
+      <c r="I15" t="s">
+        <v>60</v>
+      </c>
+      <c r="J15" t="s">
+        <v>61</v>
+      </c>
+      <c r="T15" t="s">
+        <v>72</v>
+      </c>
+      <c r="U15" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25">
+      <c r="A16" t="s">
+        <v>38</v>
+      </c>
+      <c r="E16" t="s">
+        <v>56</v>
+      </c>
+      <c r="H16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L16" t="s">
+        <v>62</v>
+      </c>
+      <c r="N16" t="s">
+        <v>63</v>
+      </c>
+      <c r="O16" t="s">
+        <v>65</v>
+      </c>
+      <c r="P16" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>68</v>
+      </c>
+      <c r="S16" t="s">
+        <v>70</v>
+      </c>
+      <c r="T16" t="s">
+        <v>73</v>
+      </c>
+      <c r="U16" t="s">
+        <v>73</v>
+      </c>
+      <c r="V16" t="s">
+        <v>76</v>
+      </c>
+      <c r="W16" t="s">
+        <v>77</v>
+      </c>
+      <c r="X16" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="17" spans="1:25">
+      <c r="A17" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="5" spans="1:16">
-      <c r="A5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C5" t="s">
+      <c r="C17" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="18" spans="1:25">
+      <c r="A18" t="s">
+        <v>40</v>
+      </c>
+      <c r="B18" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="19" spans="1:25">
+      <c r="A19" t="s">
+        <v>41</v>
+      </c>
+      <c r="B19" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="20" spans="1:25">
+      <c r="A20" t="s">
+        <v>42</v>
+      </c>
+      <c r="B20" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="21" spans="1:25">
+      <c r="A21" t="s">
         <v>43</v>
       </c>
-      <c r="F5" t="s">
+      <c r="B21" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="22" spans="1:25">
+      <c r="A22" t="s">
+        <v>44</v>
+      </c>
+      <c r="B22" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="23" spans="1:25">
+      <c r="A23" t="s">
+        <v>45</v>
+      </c>
+      <c r="B23" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="24" spans="1:25">
+      <c r="A24" t="s">
+        <v>46</v>
+      </c>
+      <c r="B24" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="25" spans="1:25">
+      <c r="A25" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="6" spans="1:16">
-      <c r="A6" t="s">
-        <v>19</v>
-      </c>
-      <c r="B6">
-        <v>255</v>
-      </c>
-      <c r="C6">
-        <v>255</v>
-      </c>
-      <c r="D6">
-        <v>255</v>
-      </c>
-      <c r="E6">
-        <v>1</v>
-      </c>
-      <c r="F6">
-        <v>255</v>
-      </c>
-      <c r="G6">
-        <v>255</v>
-      </c>
-      <c r="H6">
-        <v>255</v>
-      </c>
-      <c r="I6">
-        <v>255</v>
-      </c>
-      <c r="J6">
-        <v>255</v>
-      </c>
-      <c r="K6">
-        <v>255</v>
-      </c>
-      <c r="L6">
-        <v>255</v>
-      </c>
-      <c r="M6">
-        <v>255</v>
-      </c>
-      <c r="N6">
-        <v>255</v>
-      </c>
-      <c r="O6">
-        <v>255</v>
-      </c>
-      <c r="P6">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16">
-      <c r="A7" t="s">
-        <v>20</v>
-      </c>
-      <c r="B7" t="s">
-        <v>40</v>
-      </c>
-      <c r="C7" t="s">
-        <v>41</v>
-      </c>
-      <c r="D7" t="s">
-        <v>40</v>
-      </c>
-      <c r="E7" t="s">
-        <v>41</v>
-      </c>
-      <c r="F7" t="s">
-        <v>41</v>
-      </c>
-      <c r="G7" t="s">
-        <v>41</v>
-      </c>
-      <c r="H7" t="s">
-        <v>41</v>
-      </c>
-      <c r="I7" t="s">
-        <v>41</v>
-      </c>
-      <c r="J7" t="s">
-        <v>41</v>
-      </c>
-      <c r="K7" t="s">
-        <v>41</v>
-      </c>
-      <c r="L7" t="s">
-        <v>41</v>
-      </c>
-      <c r="M7" t="s">
-        <v>41</v>
-      </c>
-      <c r="N7" t="s">
-        <v>41</v>
-      </c>
-      <c r="O7" t="s">
-        <v>41</v>
-      </c>
-      <c r="P7" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16">
-      <c r="A8" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16">
-      <c r="A9" t="s">
-        <v>22</v>
-      </c>
-      <c r="B9" t="s">
-        <v>41</v>
-      </c>
-      <c r="C9" t="s">
-        <v>41</v>
-      </c>
-      <c r="D9" t="s">
-        <v>41</v>
-      </c>
-      <c r="E9" t="s">
-        <v>41</v>
-      </c>
-      <c r="F9" t="s">
-        <v>41</v>
-      </c>
-      <c r="G9" t="s">
-        <v>41</v>
-      </c>
-      <c r="H9" t="s">
-        <v>41</v>
-      </c>
-      <c r="I9" t="s">
-        <v>41</v>
-      </c>
-      <c r="J9" t="s">
-        <v>41</v>
-      </c>
-      <c r="K9" t="s">
-        <v>41</v>
-      </c>
-      <c r="L9" t="s">
-        <v>41</v>
-      </c>
-      <c r="M9" t="s">
-        <v>41</v>
-      </c>
-      <c r="N9" t="s">
-        <v>41</v>
-      </c>
-      <c r="O9" t="s">
-        <v>41</v>
-      </c>
-      <c r="P9" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16">
-      <c r="A10" t="s">
-        <v>23</v>
-      </c>
-      <c r="B10" t="s">
-        <v>40</v>
-      </c>
-      <c r="C10" t="s">
-        <v>40</v>
-      </c>
-      <c r="D10" t="s">
-        <v>40</v>
-      </c>
-      <c r="E10" t="s">
-        <v>40</v>
-      </c>
-      <c r="F10" t="s">
-        <v>40</v>
-      </c>
-      <c r="G10" t="s">
-        <v>40</v>
-      </c>
-      <c r="H10" t="s">
-        <v>40</v>
-      </c>
-      <c r="I10" t="s">
-        <v>40</v>
-      </c>
-      <c r="J10" t="s">
-        <v>40</v>
-      </c>
-      <c r="K10" t="s">
-        <v>40</v>
-      </c>
-      <c r="L10" t="s">
-        <v>40</v>
-      </c>
-      <c r="M10" t="s">
-        <v>40</v>
-      </c>
-      <c r="N10" t="s">
-        <v>40</v>
-      </c>
-      <c r="O10" t="s">
-        <v>40</v>
-      </c>
-      <c r="P10" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16">
-      <c r="A11" t="s">
-        <v>24</v>
-      </c>
-      <c r="D11" t="s">
-        <v>41</v>
-      </c>
-      <c r="E11" t="s">
-        <v>41</v>
-      </c>
-      <c r="F11" t="s">
-        <v>41</v>
-      </c>
-      <c r="H11" t="s">
-        <v>41</v>
-      </c>
-      <c r="I11" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16">
-      <c r="A12" t="s">
-        <v>25</v>
-      </c>
-      <c r="B12" t="s">
-        <v>41</v>
-      </c>
-      <c r="C12" t="s">
-        <v>41</v>
-      </c>
-      <c r="D12" t="s">
-        <v>41</v>
-      </c>
-      <c r="E12" t="s">
-        <v>41</v>
-      </c>
-      <c r="F12" t="s">
-        <v>41</v>
-      </c>
-      <c r="G12" t="s">
-        <v>41</v>
-      </c>
-      <c r="H12" t="s">
-        <v>41</v>
-      </c>
-      <c r="I12" t="s">
-        <v>41</v>
-      </c>
-      <c r="J12" t="s">
-        <v>41</v>
-      </c>
-      <c r="K12" t="s">
-        <v>41</v>
-      </c>
-      <c r="L12" t="s">
-        <v>41</v>
-      </c>
-      <c r="M12" t="s">
-        <v>41</v>
-      </c>
-      <c r="N12" t="s">
-        <v>41</v>
-      </c>
-      <c r="O12" t="s">
-        <v>41</v>
-      </c>
-      <c r="P12" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16">
-      <c r="A13" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16">
-      <c r="A14" t="s">
-        <v>27</v>
-      </c>
-      <c r="H14" t="s">
-        <v>51</v>
-      </c>
-      <c r="I14" t="s">
-        <v>51</v>
-      </c>
-      <c r="J14" t="s">
-        <v>51</v>
-      </c>
-      <c r="K14" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16">
-      <c r="A15" t="s">
-        <v>28</v>
-      </c>
-      <c r="H15" t="s">
-        <v>52</v>
-      </c>
-      <c r="I15" t="s">
-        <v>54</v>
-      </c>
-      <c r="J15" t="s">
-        <v>55</v>
-      </c>
-      <c r="K15" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16">
-      <c r="A16" t="s">
-        <v>29</v>
-      </c>
-      <c r="D16" t="s">
-        <v>45</v>
-      </c>
-      <c r="E16" t="s">
-        <v>46</v>
-      </c>
-      <c r="F16" t="s">
+      <c r="B25" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="26" spans="1:25">
+      <c r="A26" t="s">
         <v>48</v>
-      </c>
-      <c r="H16" t="s">
-        <v>53</v>
-      </c>
-      <c r="I16" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="17" spans="1:16">
-      <c r="A17" t="s">
-        <v>30</v>
-      </c>
-      <c r="C17" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="18" spans="1:16">
-      <c r="A18" t="s">
-        <v>31</v>
-      </c>
-      <c r="B18" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="19" spans="1:16">
-      <c r="A19" t="s">
-        <v>32</v>
-      </c>
-      <c r="B19" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="20" spans="1:16">
-      <c r="A20" t="s">
-        <v>33</v>
-      </c>
-      <c r="B20" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="21" spans="1:16">
-      <c r="A21" t="s">
-        <v>34</v>
-      </c>
-      <c r="B21" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="22" spans="1:16">
-      <c r="A22" t="s">
-        <v>35</v>
-      </c>
-      <c r="B22" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="23" spans="1:16">
-      <c r="A23" t="s">
-        <v>36</v>
-      </c>
-      <c r="B23" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="24" spans="1:16">
-      <c r="A24" t="s">
-        <v>37</v>
-      </c>
-      <c r="B24" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="25" spans="1:16">
-      <c r="A25" t="s">
-        <v>38</v>
-      </c>
-      <c r="B25" t="s">
-        <v>58</v>
       </c>
     </row>
   </sheetData>

--- a/tables/xls/it/91_Servizi.xlsx
+++ b/tables/xls/it/91_Servizi.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="90">
   <si>
     <t>NOME</t>
   </si>
@@ -54,6 +54,9 @@
     <t>OPERATORI A SUPPORTO</t>
   </si>
   <si>
+    <t>TELEFONO SEGNALANTE</t>
+  </si>
+  <si>
     <t>DATA ORA SEGNALAZIONE</t>
   </si>
   <si>
@@ -69,9 +72,6 @@
     <t>INDIRIZZO SEGNALANTE</t>
   </si>
   <si>
-    <t>TELEFONO SEGNALANTE</t>
-  </si>
-  <si>
     <t>LATITUDINE</t>
   </si>
   <si>
@@ -90,6 +90,15 @@
     <t>NOTE</t>
   </si>
   <si>
+    <t>COGNOME REFERENTE</t>
+  </si>
+  <si>
+    <t>NOME REFERENTE</t>
+  </si>
+  <si>
+    <t>TELEFONO REFERENTE</t>
+  </si>
+  <si>
     <t>Sequenza</t>
   </si>
   <si>
@@ -207,6 +216,12 @@
     <t>Squadre/gruppi attivati, una per riga</t>
   </si>
   <si>
+    <t>TEL. SEGNALANTE</t>
+  </si>
+  <si>
+    <t>Numero di telefono del segnalante</t>
+  </si>
+  <si>
     <t>Data e ora in cui è arrivata la segnalazione (diversa da INIZIO, che è l'avvio dell'intervento)</t>
   </si>
   <si>
@@ -225,12 +240,6 @@
     <t>Ruolo di chi ha effettuato la segnalazione</t>
   </si>
   <si>
-    <t>TEL. SEGNALANTE</t>
-  </si>
-  <si>
-    <t>Numero di telefono del segnalante</t>
-  </si>
-  <si>
     <t>Numero Decimale</t>
   </si>
   <si>
@@ -256,6 +265,15 @@
   </si>
   <si>
     <t>Verrà utilizzato per identificare il servizio sulla mappa</t>
+  </si>
+  <si>
+    <t>COGNOME REF.</t>
+  </si>
+  <si>
+    <t>NOME REF.</t>
+  </si>
+  <si>
+    <t>TELEFONO REF.</t>
   </si>
   <si>
     <t>SERVIZI</t>
@@ -607,7 +625,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:X1"/>
+  <dimension ref="A1:AA1"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="5.856" bestFit="true" customWidth="true" style="0"/>
@@ -622,21 +640,24 @@
     <col min="10" max="10" width="11.711" bestFit="true" customWidth="true" style="0"/>
     <col min="11" max="11" width="19.995" bestFit="true" customWidth="true" style="0"/>
     <col min="12" max="12" width="24.708" bestFit="true" customWidth="true" style="0"/>
-    <col min="13" max="13" width="25.851" bestFit="true" customWidth="true" style="0"/>
-    <col min="14" max="14" width="18.71" bestFit="true" customWidth="true" style="0"/>
+    <col min="13" max="13" width="23.423" bestFit="true" customWidth="true" style="0"/>
+    <col min="14" max="14" width="25.851" bestFit="true" customWidth="true" style="0"/>
     <col min="15" max="15" width="18.71" bestFit="true" customWidth="true" style="0"/>
-    <col min="16" max="16" width="24.708" bestFit="true" customWidth="true" style="0"/>
+    <col min="16" max="16" width="18.71" bestFit="true" customWidth="true" style="0"/>
     <col min="17" max="17" width="24.708" bestFit="true" customWidth="true" style="0"/>
-    <col min="18" max="18" width="23.423" bestFit="true" customWidth="true" style="0"/>
+    <col min="18" max="18" width="24.708" bestFit="true" customWidth="true" style="0"/>
     <col min="19" max="19" width="12.854" bestFit="true" customWidth="true" style="0"/>
     <col min="20" max="20" width="13.997" bestFit="true" customWidth="true" style="0"/>
     <col min="21" max="21" width="8.141" bestFit="true" customWidth="true" style="0"/>
     <col min="22" max="22" width="9.283" bestFit="true" customWidth="true" style="0"/>
     <col min="23" max="23" width="8.141" bestFit="true" customWidth="true" style="0"/>
     <col min="24" max="24" width="5.856" bestFit="true" customWidth="true" style="0"/>
+    <col min="25" max="25" width="21.138" bestFit="true" customWidth="true" style="0"/>
+    <col min="26" max="26" width="17.567" bestFit="true" customWidth="true" style="0"/>
+    <col min="27" max="27" width="22.28" bestFit="true" customWidth="true" style="0"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24">
+    <row r="1" spans="1:27">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -708,6 +729,15 @@
       </c>
       <c r="X1" t="s">
         <v>23</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -722,10 +752,10 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:Y26"/>
+  <dimension ref="A1:AB26"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
-    <row r="1" spans="1:25">
+    <row r="1" spans="1:28">
       <c r="B1" t="s">
         <v>0</v>
       </c>
@@ -798,10 +828,19 @@
       <c r="Y1" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="2" spans="1:25">
+      <c r="Z1" t="s">
+        <v>24</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="2" spans="1:28">
       <c r="A2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B2">
         <v>1</v>
@@ -840,28 +879,28 @@
         <v>16</v>
       </c>
       <c r="N2">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="O2">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="P2">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="Q2">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="R2">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="S2">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="T2">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="U2">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="V2">
         <v>80</v>
@@ -875,10 +914,19 @@
       <c r="Y2">
         <v>99</v>
       </c>
-    </row>
-    <row r="3" spans="1:25">
+      <c r="Z2">
+        <v>100</v>
+      </c>
+      <c r="AA2">
+        <v>101</v>
+      </c>
+      <c r="AB2">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="3" spans="1:28">
       <c r="A3" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B3" t="s">
         <v>0</v>
@@ -917,13 +965,13 @@
         <v>11</v>
       </c>
       <c r="N3" t="s">
-        <v>12</v>
+        <v>66</v>
       </c>
       <c r="O3" t="s">
-        <v>64</v>
+        <v>13</v>
       </c>
       <c r="P3" t="s">
-        <v>14</v>
+        <v>69</v>
       </c>
       <c r="Q3" t="s">
         <v>15</v>
@@ -932,7 +980,7 @@
         <v>16</v>
       </c>
       <c r="S3" t="s">
-        <v>69</v>
+        <v>17</v>
       </c>
       <c r="T3" t="s">
         <v>18</v>
@@ -952,104 +1000,122 @@
       <c r="Y3" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="4" spans="1:25">
+      <c r="Z3" t="s">
+        <v>83</v>
+      </c>
+      <c r="AA3" t="s">
+        <v>84</v>
+      </c>
+      <c r="AB3" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="4" spans="1:28">
       <c r="A4" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B4" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D4" t="s">
+        <v>56</v>
+      </c>
+      <c r="E4" t="s">
+        <v>56</v>
+      </c>
+      <c r="F4" t="s">
+        <v>60</v>
+      </c>
+      <c r="G4" t="s">
+        <v>60</v>
+      </c>
+      <c r="H4" t="s">
+        <v>60</v>
+      </c>
+      <c r="I4" t="s">
         <v>52</v>
       </c>
-      <c r="D4" t="s">
-        <v>53</v>
-      </c>
-      <c r="E4" t="s">
-        <v>53</v>
-      </c>
-      <c r="F4" t="s">
+      <c r="J4" t="s">
+        <v>52</v>
+      </c>
+      <c r="K4" t="s">
+        <v>52</v>
+      </c>
+      <c r="L4" t="s">
+        <v>55</v>
+      </c>
+      <c r="M4" t="s">
+        <v>55</v>
+      </c>
+      <c r="N4" t="s">
+        <v>52</v>
+      </c>
+      <c r="O4" t="s">
+        <v>60</v>
+      </c>
+      <c r="P4" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>52</v>
+      </c>
+      <c r="R4" t="s">
+        <v>56</v>
+      </c>
+      <c r="S4" t="s">
+        <v>52</v>
+      </c>
+      <c r="T4" t="s">
+        <v>74</v>
+      </c>
+      <c r="U4" t="s">
+        <v>74</v>
+      </c>
+      <c r="V4" t="s">
+        <v>78</v>
+      </c>
+      <c r="W4" t="s">
+        <v>52</v>
+      </c>
+      <c r="X4" t="s">
+        <v>56</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>55</v>
+      </c>
+      <c r="Z4" t="s">
+        <v>52</v>
+      </c>
+      <c r="AA4" t="s">
+        <v>52</v>
+      </c>
+      <c r="AB4" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="5" spans="1:28">
+      <c r="A5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D5" t="s">
         <v>57</v>
       </c>
-      <c r="G4" t="s">
-        <v>57</v>
-      </c>
-      <c r="H4" t="s">
-        <v>57</v>
-      </c>
-      <c r="I4" t="s">
-        <v>49</v>
-      </c>
-      <c r="J4" t="s">
-        <v>49</v>
-      </c>
-      <c r="K4" t="s">
-        <v>49</v>
-      </c>
-      <c r="L4" t="s">
-        <v>52</v>
-      </c>
-      <c r="M4" t="s">
-        <v>52</v>
-      </c>
-      <c r="N4" t="s">
-        <v>57</v>
-      </c>
-      <c r="O4" t="s">
-        <v>49</v>
-      </c>
-      <c r="P4" t="s">
-        <v>49</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>53</v>
-      </c>
-      <c r="R4" t="s">
-        <v>49</v>
-      </c>
-      <c r="S4" t="s">
-        <v>49</v>
-      </c>
-      <c r="T4" t="s">
-        <v>71</v>
-      </c>
-      <c r="U4" t="s">
-        <v>71</v>
-      </c>
-      <c r="V4" t="s">
-        <v>75</v>
-      </c>
-      <c r="W4" t="s">
-        <v>49</v>
-      </c>
-      <c r="X4" t="s">
-        <v>53</v>
-      </c>
-      <c r="Y4" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="5" spans="1:25">
-      <c r="A5" t="s">
-        <v>27</v>
-      </c>
-      <c r="D5" t="s">
-        <v>54</v>
-      </c>
       <c r="E5" t="s">
-        <v>55</v>
-      </c>
-      <c r="Q5" t="s">
-        <v>67</v>
+        <v>58</v>
+      </c>
+      <c r="R5" t="s">
+        <v>72</v>
       </c>
       <c r="X5" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="6" spans="1:25">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="6" spans="1:28">
       <c r="A6" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B6">
         <v>255</v>
@@ -1123,516 +1189,561 @@
       <c r="Y6">
         <v>255</v>
       </c>
-    </row>
-    <row r="7" spans="1:25">
+      <c r="Z6">
+        <v>255</v>
+      </c>
+      <c r="AA6">
+        <v>255</v>
+      </c>
+      <c r="AB6">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="7" spans="1:28">
       <c r="A7" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B7" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C7" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="D7" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E7" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="F7" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="G7" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="H7" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="I7" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="J7" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="K7" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="L7" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="M7" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="N7" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="O7" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="P7" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="Q7" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="R7" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="S7" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="T7" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="U7" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="V7" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="W7" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="X7" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="Y7" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="8" spans="1:25">
+        <v>54</v>
+      </c>
+      <c r="Z7" t="s">
+        <v>54</v>
+      </c>
+      <c r="AA7" t="s">
+        <v>54</v>
+      </c>
+      <c r="AB7" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="8" spans="1:28">
       <c r="A8" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="9" spans="1:25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="9" spans="1:28">
       <c r="A9" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B9" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C9" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="D9" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E9" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="F9" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="G9" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="H9" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="I9" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="J9" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="K9" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="L9" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="M9" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="N9" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="O9" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="P9" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="Q9" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="R9" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="S9" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="T9" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="U9" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="V9" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="W9" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="X9" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="Y9" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="10" spans="1:25">
+        <v>54</v>
+      </c>
+      <c r="Z9" t="s">
+        <v>54</v>
+      </c>
+      <c r="AA9" t="s">
+        <v>54</v>
+      </c>
+      <c r="AB9" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="10" spans="1:28">
       <c r="A10" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B10" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C10" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="D10" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="E10" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="F10" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="G10" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="H10" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="I10" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="J10" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K10" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="L10" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="M10" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="N10" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="O10" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="P10" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="Q10" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="R10" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="S10" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="T10" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="U10" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="V10" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="W10" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="X10" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="Y10" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="11" spans="1:25">
+        <v>53</v>
+      </c>
+      <c r="Z10" t="s">
+        <v>53</v>
+      </c>
+      <c r="AA10" t="s">
+        <v>53</v>
+      </c>
+      <c r="AB10" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="11" spans="1:28">
       <c r="A11" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E11" t="s">
-        <v>51</v>
-      </c>
-      <c r="O11" t="s">
-        <v>51</v>
+        <v>54</v>
+      </c>
+      <c r="N11" t="s">
+        <v>54</v>
       </c>
       <c r="P11" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="Q11" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="R11" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="S11" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="T11" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="U11" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="V11" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="W11" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="X11" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="12" spans="1:25">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="12" spans="1:28">
       <c r="A12" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B12" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C12" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="D12" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E12" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="F12" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="G12" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="H12" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="I12" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="J12" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="K12" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="L12" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="M12" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="N12" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="O12" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="P12" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="Q12" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="R12" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="S12" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="T12" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="U12" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="V12" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="W12" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="X12" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="Y12" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="13" spans="1:25">
+        <v>54</v>
+      </c>
+      <c r="Z12" t="s">
+        <v>54</v>
+      </c>
+      <c r="AA12" t="s">
+        <v>54</v>
+      </c>
+      <c r="AB12" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="13" spans="1:28">
       <c r="A13" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="14" spans="1:25">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="14" spans="1:28">
       <c r="A14" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="I14" t="s">
+        <v>62</v>
+      </c>
+      <c r="J14" t="s">
+        <v>62</v>
+      </c>
+      <c r="T14" t="s">
+        <v>62</v>
+      </c>
+      <c r="U14" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="15" spans="1:28">
+      <c r="A15" t="s">
+        <v>40</v>
+      </c>
+      <c r="I15" t="s">
+        <v>63</v>
+      </c>
+      <c r="J15" t="s">
+        <v>64</v>
+      </c>
+      <c r="T15" t="s">
+        <v>75</v>
+      </c>
+      <c r="U15" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="16" spans="1:28">
+      <c r="A16" t="s">
+        <v>41</v>
+      </c>
+      <c r="E16" t="s">
         <v>59</v>
       </c>
-      <c r="J14" t="s">
-        <v>59</v>
-      </c>
-      <c r="T14" t="s">
-        <v>59</v>
-      </c>
-      <c r="U14" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="15" spans="1:25">
-      <c r="A15" t="s">
-        <v>37</v>
-      </c>
-      <c r="I15" t="s">
-        <v>60</v>
-      </c>
-      <c r="J15" t="s">
+      <c r="H16" t="s">
         <v>61</v>
       </c>
-      <c r="T15" t="s">
-        <v>72</v>
-      </c>
-      <c r="U15" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="16" spans="1:25">
-      <c r="A16" t="s">
-        <v>38</v>
-      </c>
-      <c r="E16" t="s">
-        <v>56</v>
-      </c>
-      <c r="H16" t="s">
-        <v>58</v>
-      </c>
       <c r="L16" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="N16" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="O16" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="P16" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="Q16" t="s">
-        <v>68</v>
-      </c>
-      <c r="S16" t="s">
-        <v>70</v>
+        <v>71</v>
+      </c>
+      <c r="R16" t="s">
+        <v>73</v>
       </c>
       <c r="T16" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="U16" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="V16" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="W16" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="X16" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="17" spans="1:25">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="17" spans="1:28">
       <c r="A17" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C17" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="18" spans="1:25">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="18" spans="1:28">
       <c r="A18" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B18" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="19" spans="1:25">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="19" spans="1:28">
       <c r="A19" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B19" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="20" spans="1:25">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="20" spans="1:28">
       <c r="A20" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B20" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="21" spans="1:25">
+    <row r="21" spans="1:28">
       <c r="A21" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B21" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="22" spans="1:25">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="22" spans="1:28">
       <c r="A22" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B22" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="23" spans="1:28">
+      <c r="A23" t="s">
+        <v>48</v>
+      </c>
+      <c r="B23" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="24" spans="1:28">
+      <c r="A24" t="s">
+        <v>49</v>
+      </c>
+      <c r="B24" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="25" spans="1:28">
+      <c r="A25" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="23" spans="1:25">
-      <c r="A23" t="s">
-        <v>45</v>
-      </c>
-      <c r="B23" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="24" spans="1:25">
-      <c r="A24" t="s">
-        <v>46</v>
-      </c>
-      <c r="B24" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="25" spans="1:25">
-      <c r="A25" t="s">
-        <v>47</v>
-      </c>
       <c r="B25" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="26" spans="1:25">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="26" spans="1:28">
       <c r="A26" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
     </row>
   </sheetData>
